--- a/23-24_KBL_stats.xlsx
+++ b/23-24_KBL_stats.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30009"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30013"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Project\2026\KBL Stats Analyzer 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151698F9-F335-408F-A55C-9BB173326144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554185DC-C6B1-4C80-B1F6-A10AFC7BDDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C857A6F3-DAC3-47BF-9FFB-2634F9EBE6C3}"/>
   </bookViews>

--- a/23-24_KBL_stats.xlsx
+++ b/23-24_KBL_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Project\2026\KBL Stats Analyzer 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DB48A2-2437-4672-BB05-49D095CAC3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF60D93-A11F-4438-A279-6EFD75227772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{C857A6F3-DAC3-47BF-9FFB-2634F9EBE6C3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="308">
   <si>
     <t>Season</t>
   </si>
@@ -10498,6 +10498,9 @@
       <c r="BP33" s="21">
         <v>48000</v>
       </c>
+      <c r="BQ33" s="30" t="s">
+        <v>305</v>
+      </c>
       <c r="BU33" s="35"/>
       <c r="BV33" s="35"/>
       <c r="BW33" s="35"/>
